--- a/Lab_4/data/partB/param_optimization_process/v100_k40_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k40_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -591,28 +591,28 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,28 +677,28 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -707,16 +707,16 @@
         <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -729,7 +729,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -738,16 +738,16 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -759,16 +759,16 @@
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -830,49 +830,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
         <v>9</v>
       </c>
-      <c r="G8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H8" t="n">
-        <v>13</v>
-      </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -900,22 +900,22 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
         <v>3</v>
@@ -924,7 +924,7 @@
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1010,22 +1010,22 @@
         <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1062,22 +1062,22 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -1117,19 +1117,19 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
         <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1145,7 +1145,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1154,16 +1154,16 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1172,19 +1172,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
         <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15360,7 +15360,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19916,7 +19916,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21242,7 @@
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25560,7 +25560,7 @@
       </c>
       <c r="C1427" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
